--- a/notebooks/ARIMAX/predictions_afr.xlsx
+++ b/notebooks/ARIMAX/predictions_afr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\balot\DataAndModels\notebooks\ARIMAX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042FAD43-4E64-446C-95A4-7F01D782EBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D590637-CCBC-4453-A7D1-D8C49CAEF3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
